--- a/Results/- Hash Perceptual.xlsx
+++ b/Results/- Hash Perceptual.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37C5C0D-A6DA-4E63-8859-C05E37FC128A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19E581F-9935-4F78-8F52-EB20A722C28B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="22" r:id="rId1"/>
@@ -42,8 +42,45 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="2">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="371">
   <si>
     <t>Imagem Original</t>
   </si>
@@ -1286,6 +1323,68 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>7</v>
+    <v>8</v>
+    <v>1</v>
+    <v>1</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_error">
+    <k n="colOffset" t="i"/>
+    <k n="errorType" t="i"/>
+    <k n="rwOffset" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
+</rvStructures>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1677,8 +1776,9 @@
       <c r="K2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>33</v>
+      <c r="L2" s="3" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="L2" ca="1">F10:M11</f>
+        <v>#VALUE!</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>35</v>
